--- a/data/trans_dic/P25C_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 11,98</t>
+          <t>1,61; 11,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,39</t>
+          <t>0,67; 4,75</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 11,34</t>
+          <t>1,66; 10,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,43</t>
+          <t>0,93; 4,92</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,06</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,21</t>
+          <t>1,0; 5,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,1</t>
+          <t>0,73; 7,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,69</t>
+          <t>1,27; 4,43</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,15</t>
+          <t>1,11; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,79</t>
+          <t>2,63; 11,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,73</t>
+          <t>2,29; 7,51</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,96</t>
+          <t>0,0; 73,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,81</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 12,67</t>
+          <t>1,02; 13,96</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,85</t>
+          <t>0,58; 2,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,95</t>
+          <t>2,59; 5,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,22</t>
+          <t>1,09; 3,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2882</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>689; 7790</t>
+          <t>1048; 7211</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1227; 8267</t>
+          <t>1255; 8941</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4203</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>826; 6430</t>
+          <t>939; 5949</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1458; 8141</t>
+          <t>1395; 7379</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 15154</t>
+          <t>0; 14374</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2849</t>
+          <t>0; 2816</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 14894</t>
+          <t>0; 14959</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2056; 9869</t>
+          <t>1884; 10525</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>582; 5608</t>
+          <t>578; 5766</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3778; 12592</t>
+          <t>3420; 11877</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>972; 7176</t>
+          <t>981; 7120</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1823; 8269</t>
+          <t>1844; 8206</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3718; 12236</t>
+          <t>3627; 11888</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4951</t>
+          <t>0; 5163</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3282</t>
+          <t>0; 2310</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>431; 5605</t>
+          <t>449; 6176</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5742; 23925</t>
+          <t>4834; 23474</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8638; 19622</t>
+          <t>8537; 19317</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11471; 37745</t>
+          <t>12701; 38956</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,09</t>
+          <t>1,04; 10,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,75</t>
+          <t>0,65; 4,16</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,49</t>
+          <t>2,09; 12,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,92</t>
+          <t>0,87; 5,32</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,75; 7,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>1,08; 6,72</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,56</t>
+          <t>1,1; 5,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,3</t>
+          <t>0,85; 7,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,43</t>
+          <t>1,3; 4,64</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 8,08</t>
+          <t>0,78; 7,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,7</t>
+          <t>2,3; 10,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,51</t>
+          <t>2,15; 7,4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,99</t>
+          <t>0,0; 71,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 13,96</t>
+          <t>1,09; 12,35</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,79</t>
+          <t>1,34; 3,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,86</t>
+          <t>2,46; 5,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,33</t>
+          <t>2,1; 3,9</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>696</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3786</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>0; 3284</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1048; 7211</t>
+          <t>719; 7510</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1255; 8941</t>
+          <t>1298; 8316</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>4129</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>0; 3562</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>939; 5949</t>
+          <t>1316; 7733</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1395; 7379</t>
+          <t>1439; 8792</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>665</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3906</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 14374</t>
+          <t>793; 7407</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2816</t>
+          <t>0; 3141</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 14959</t>
+          <t>1383; 8575</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7807</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1884; 10525</t>
+          <t>2325; 11325</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>578; 5766</t>
+          <t>725; 6200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3420; 11877</t>
+          <t>3856; 13730</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7233</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>981; 7120</t>
+          <t>733; 7406</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1844; 8206</t>
+          <t>1838; 8499</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3627; 11888</t>
+          <t>3743; 12878</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>498</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1931</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5163</t>
+          <t>0; 4765</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2310</t>
+          <t>0; 2439</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>449; 6176</t>
+          <t>491; 5536</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28793</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4834; 23474</t>
+          <t>8735; 22362</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8537; 19317</t>
+          <t>8805; 21085</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12701; 38956</t>
+          <t>21167; 39298</t>
         </is>
       </c>
     </row>
